--- a/data/拜谱单细胞实验预约.xlsx
+++ b/data/拜谱单细胞实验预约.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
   <si>
     <t>填表日期</t>
   </si>
@@ -74,7 +74,7 @@
     <t>上机方式</t>
   </si>
   <si>
-    <t>委托单编号</t>
+    <t>项目编号</t>
   </si>
   <si>
     <t>样本接收日期</t>
@@ -95,111 +95,60 @@
     <t>备注2</t>
   </si>
   <si>
-    <t>BPC202602144</t>
-  </si>
-  <si>
-    <t>YP20260504403</t>
-  </si>
-  <si>
-    <t>康文军</t>
-  </si>
-  <si>
-    <t>川北医学院附属医院</t>
-  </si>
-  <si>
-    <t>甘媛琳</t>
+    <t>BPVC202600205</t>
+  </si>
+  <si>
+    <t>YP20260504580</t>
+  </si>
+  <si>
+    <t>李智</t>
+  </si>
+  <si>
+    <t>上海市同济医院</t>
+  </si>
+  <si>
+    <t>陈老师</t>
+  </si>
+  <si>
+    <t>小鼠</t>
+  </si>
+  <si>
+    <t>肝脏组织</t>
+  </si>
+  <si>
+    <t>组织解离</t>
+  </si>
+  <si>
+    <t>4度</t>
+  </si>
+  <si>
+    <t>10X 3'GEM-X单细胞（单细胞核）转录组 质控版</t>
+  </si>
+  <si>
+    <t>BP-G260505743</t>
+  </si>
+  <si>
+    <t>正常上机</t>
+  </si>
+  <si>
+    <t>BPC202505466</t>
+  </si>
+  <si>
+    <t>YP20260504586</t>
+  </si>
+  <si>
+    <t>王丽</t>
+  </si>
+  <si>
+    <t>创芯生物</t>
+  </si>
+  <si>
+    <t>陈博</t>
   </si>
   <si>
     <t>人</t>
   </si>
   <si>
-    <t>肠炎组织</t>
-  </si>
-  <si>
-    <t>组织解离</t>
-  </si>
-  <si>
-    <t>冷链4度</t>
-  </si>
-  <si>
-    <t>10x 3'NEXT-GEM单细胞（单细胞核）转录组 标准分析版（Illumina平台）</t>
-  </si>
-  <si>
-    <t>BP-G260505472</t>
-  </si>
-  <si>
-    <t>正常上机</t>
-  </si>
-  <si>
-    <t>BPC202504877</t>
-  </si>
-  <si>
-    <t>YP20260504587</t>
-  </si>
-  <si>
-    <t>曹丽如</t>
-  </si>
-  <si>
-    <t>复旦大学附属中山医院</t>
-  </si>
-  <si>
-    <t>郭老师</t>
-  </si>
-  <si>
-    <t>小鼠</t>
-  </si>
-  <si>
-    <t>肝脏组织</t>
-  </si>
-  <si>
-    <t>4度</t>
-  </si>
-  <si>
-    <t>10x 3'GEM-X单细胞（单细胞核）转录组 质控版</t>
-  </si>
-  <si>
-    <t>BP-G260505777</t>
-  </si>
-  <si>
-    <t>flox组活率30%左右，ko组活率70%左右，不满足上机要求</t>
-  </si>
-  <si>
-    <t>BPVC202600205</t>
-  </si>
-  <si>
-    <t>YP20260504580</t>
-  </si>
-  <si>
-    <t>李智</t>
-  </si>
-  <si>
-    <t>上海市同济医院</t>
-  </si>
-  <si>
-    <t>陈老师</t>
-  </si>
-  <si>
-    <t>10X 3'GEM-X单细胞（单细胞核）转录组 质控版</t>
-  </si>
-  <si>
-    <t>BP-G260505743</t>
-  </si>
-  <si>
-    <t>BPC202505466</t>
-  </si>
-  <si>
-    <t>YP20260504586</t>
-  </si>
-  <si>
-    <t>王丽</t>
-  </si>
-  <si>
-    <t>创芯生物</t>
-  </si>
-  <si>
-    <t>陈博</t>
-  </si>
-  <si>
     <t>肺组织</t>
   </si>
   <si>
@@ -210,31 +159,6 @@
   </si>
   <si>
     <t>1例正常上机，1例荧光偏黄，低风险上机</t>
-  </si>
-  <si>
-    <t>YP20260504638</t>
-  </si>
-  <si>
-    <t>10x 3'NEXT-GEM单细胞（单细胞核）转录组 标准分析版（真迈平台），做到建库
-，不上机</t>
-  </si>
-  <si>
-    <t>BP-G260505866</t>
-  </si>
-  <si>
-    <t>第一批样本的2例活率不满足上机要求，第二批2例低风险上机</t>
-  </si>
-  <si>
-    <t>YP20260504677</t>
-  </si>
-  <si>
-    <t>肺穿刺组织</t>
-  </si>
-  <si>
-    <t>BP-G260505905</t>
-  </si>
-  <si>
-    <t>显微镜下细胞凋亡，台盼蓝染色明显。荧光计数活率虽然较高但已经没有参考意义，悬液不满足上机要求</t>
   </si>
   <si>
     <t>BPVC202600175</t>
@@ -272,7 +196,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -306,13 +230,6 @@
       <sz val="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFC00000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -834,155 +751,155 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1017,9 +934,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1558,8 +1472,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V8"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="12.75" outlineLevelRow="7"/>
+  <dimension ref="A1:V4"/>
+  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="12.75" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="4" width="17.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="16.2857142857143" customWidth="1"/>
@@ -1648,15 +1562,17 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="11.25" spans="1:22">
       <c r="A2" s="10">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="B2" s="10">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="C2" s="10">
-        <v>46151</v>
-      </c>
-      <c r="D2" s="1"/>
+        <v>46156</v>
+      </c>
+      <c r="D2" s="10">
+        <v>46156</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>22</v>
       </c>
@@ -1679,7 +1595,7 @@
         <v>28</v>
       </c>
       <c r="L2" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>29</v>
@@ -1694,13 +1610,13 @@
         <v>32</v>
       </c>
       <c r="Q2" s="11">
-        <v>46151.6236111111</v>
+        <v>46156.6284722222</v>
       </c>
       <c r="R2" s="10">
-        <v>46151</v>
+        <v>46156</v>
       </c>
       <c r="S2" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>33</v>
@@ -1708,15 +1624,17 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="11.25" spans="1:22">
       <c r="A3" s="10">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B3" s="10">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="10">
         <v>46156</v>
       </c>
-      <c r="D3" s="1"/>
+      <c r="D3" s="10">
+        <v>46156</v>
+      </c>
       <c r="E3" s="1" t="s">
         <v>34</v>
       </c>
@@ -1739,341 +1657,93 @@
         <v>40</v>
       </c>
       <c r="L3" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>29</v>
       </c>
       <c r="N3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="Q3" s="11">
-        <v>46156.5381944444</v>
+        <v>46156.5326388889</v>
       </c>
       <c r="R3" s="10">
         <v>46156</v>
       </c>
       <c r="S3" s="1">
-        <v>0</v>
-      </c>
-      <c r="T3" s="12" t="s">
-        <v>44</v>
+        <v>2</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="11.25" spans="1:22">
       <c r="A4" s="10">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B4" s="10">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="C4" s="10">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="D4" s="10">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="L4" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>29</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="O4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P4" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="11">
+        <v>46161.5076388889</v>
+      </c>
+      <c r="R4" s="10">
+        <v>46161</v>
+      </c>
+      <c r="S4" s="1">
+        <v>6</v>
+      </c>
+      <c r="T4" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>46156.6284722222</v>
-      </c>
-      <c r="R4" s="10">
-        <v>46156</v>
-      </c>
-      <c r="S4" s="1">
-        <v>4</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="11.25" spans="1:22">
-      <c r="A5" s="10">
-        <v>46156</v>
-      </c>
-      <c r="B5" s="10">
-        <v>46155</v>
-      </c>
-      <c r="C5" s="10">
-        <v>46156</v>
-      </c>
-      <c r="D5" s="10">
-        <v>46156</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L5" s="1">
-        <v>2</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>46156.5326388889</v>
-      </c>
-      <c r="R5" s="10">
-        <v>46156</v>
-      </c>
-      <c r="S5" s="1">
-        <v>2</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="11.25" spans="1:22">
-      <c r="A6" s="10">
-        <v>46157</v>
-      </c>
-      <c r="B6" s="10">
-        <v>46156</v>
-      </c>
-      <c r="C6" s="10">
-        <v>46157</v>
-      </c>
-      <c r="D6" s="10">
-        <v>46157</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L6" s="1">
-        <v>4</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>46157.5548611111</v>
-      </c>
-      <c r="R6" s="10">
-        <v>46157</v>
-      </c>
-      <c r="S6" s="1">
-        <v>2</v>
-      </c>
-      <c r="T6" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="11.25" spans="1:22">
-      <c r="A7" s="10">
-        <v>46157</v>
-      </c>
-      <c r="B7" s="10">
-        <v>46157</v>
-      </c>
-      <c r="C7" s="10">
-        <v>46157</v>
-      </c>
-      <c r="D7" s="10">
-        <v>46157</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q7" s="11">
-        <v>46157.76875</v>
-      </c>
-      <c r="R7" s="10">
-        <v>46157</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="11.25" spans="1:22">
-      <c r="A8" s="10">
-        <v>46157</v>
-      </c>
-      <c r="B8" s="10">
-        <v>46161</v>
-      </c>
-      <c r="C8" s="10">
-        <v>46161</v>
-      </c>
-      <c r="D8" s="10">
-        <v>46161</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L8" s="1">
-        <v>6</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>46161.5076388889</v>
-      </c>
-      <c r="R8" s="10">
-        <v>46161</v>
-      </c>
-      <c r="S8" s="1">
-        <v>6</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
